--- a/utils/monday_sprint_sprint_2024-44.xlsx
+++ b/utils/monday_sprint_sprint_2024-44.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="163">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>27476</t>
+    <t>7243146411</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,7 +87,7 @@
     <t>16/08/2024</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>04/09/2024</t>
   </si>
   <si>
     <t>Feito</t>
@@ -102,34 +102,37 @@
     <t>Agosto</t>
   </si>
   <si>
-    <t>26830</t>
+    <t>7360200600</t>
   </si>
   <si>
     <t>Segregação custeiro - Acabamento - Tratamento térmico</t>
   </si>
   <si>
-    <t>04/09/2024</t>
+    <t>03/09/2024</t>
   </si>
   <si>
     <t>A fazer</t>
   </si>
   <si>
-    <t>Aberto</t>
-  </si>
-  <si>
     <t>Semana 1</t>
   </si>
   <si>
     <t>Setembro</t>
   </si>
   <si>
+    <t>7360200632</t>
+  </si>
+  <si>
     <t>Segregação custeiro - Acabamento - Rebarbação</t>
   </si>
   <si>
+    <t>7360200660</t>
+  </si>
+  <si>
     <t>Segregação custeiro - Acabamento - Apoio industrial</t>
   </si>
   <si>
-    <t>27176</t>
+    <t>7369069472</t>
   </si>
   <si>
     <t>PDI Inspeção, status do laudo.</t>
@@ -141,31 +144,49 @@
     <t>Fazendo</t>
   </si>
   <si>
+    <t>7369064358</t>
+  </si>
+  <si>
     <t>PDI Inspeção, mínimo e máximo dentro do intervalo da dimensão.</t>
   </si>
   <si>
+    <t>15/09/2024</t>
+  </si>
+  <si>
+    <t>7369084436</t>
+  </si>
+  <si>
     <t>PDI Relatório de inspeção</t>
   </si>
   <si>
-    <t>27379</t>
+    <t>10/09/2024</t>
+  </si>
+  <si>
+    <t>7403657021</t>
   </si>
   <si>
     <t>Bloquear o reprocessamento período setembro/2023 a agosto/2024</t>
   </si>
   <si>
-    <t>10/09/2024</t>
+    <t>09/09/2024</t>
   </si>
   <si>
     <t>Semana 2</t>
   </si>
   <si>
+    <t>7403643900</t>
+  </si>
+  <si>
     <t>Rotina para importar planilha do cálculo do custos ajustada.</t>
   </si>
   <si>
+    <t>7403622204</t>
+  </si>
+  <si>
     <t>Novo tipo de dados para embalagens “EMB.USI”.</t>
   </si>
   <si>
-    <t>27648</t>
+    <t>7333932563</t>
   </si>
   <si>
     <t>APONTAMENTO TABLET MANIPULADORES</t>
@@ -177,13 +198,13 @@
     <t>Semana 5</t>
   </si>
   <si>
-    <t>27327</t>
+    <t>7242726786</t>
   </si>
   <si>
     <t>Melhoria sistema de modelo II</t>
   </si>
   <si>
-    <t>27610</t>
+    <t>7327697549</t>
   </si>
   <si>
     <t>Amostras Alto Impacto (Fundição adicional de Seriadas)</t>
@@ -192,94 +213,106 @@
     <t>29/08/2024</t>
   </si>
   <si>
-    <t>27573</t>
+    <t>7327821010</t>
   </si>
   <si>
     <t>Aumento de caracter</t>
   </si>
   <si>
-    <t>27619</t>
+    <t>7333946564</t>
   </si>
   <si>
     <t>Inclusão de registro de Trocas</t>
   </si>
   <si>
-    <t>27522</t>
+    <t>7334004911</t>
   </si>
   <si>
     <t>Melhoria Cartoteca geral de pedidos</t>
   </si>
   <si>
-    <t>27636</t>
+    <t>7327675531</t>
   </si>
   <si>
     <t>Razão Crítica</t>
   </si>
   <si>
-    <t>27611</t>
+    <t>7327684909</t>
   </si>
   <si>
     <t>E-mail automático após movimentação</t>
   </si>
   <si>
-    <t>27380</t>
+    <t>7334325292</t>
   </si>
   <si>
     <t>Inclusão de Check List de Liberação para Talhas Elétricas</t>
   </si>
   <si>
-    <t>27378</t>
+    <t>12/09/2024</t>
+  </si>
+  <si>
+    <t>7334335476</t>
   </si>
   <si>
     <t>[COMRAS] Criação da tela de ressuprimento: Lista de materiais ressuprimento via estoque minimo</t>
   </si>
   <si>
+    <t>7359911112</t>
+  </si>
+  <si>
     <t>Criar tela para lançar o frete e vincular quando a nota já estiver lançada</t>
   </si>
   <si>
-    <t>27525</t>
+    <t>7327715150</t>
   </si>
   <si>
     <t>Inserir Coluna "Dalca/Lianco"</t>
   </si>
   <si>
-    <t>27682</t>
+    <t>7331945381</t>
   </si>
   <si>
     <t>Alteração de operação (Reb VI e VII)</t>
   </si>
   <si>
-    <t>27421</t>
+    <t>7359958791</t>
   </si>
   <si>
     <t>Tela de conferencia</t>
   </si>
   <si>
-    <t>24256</t>
+    <t>7369642514</t>
   </si>
   <si>
     <t>PADRONIZAR APLICAÇÃO 5S</t>
   </si>
   <si>
-    <t>27128</t>
+    <t>7332189430</t>
   </si>
   <si>
     <t>Preenchimento Razão Crítica</t>
   </si>
   <si>
+    <t>11/09/2024</t>
+  </si>
+  <si>
     <t>Implantação</t>
   </si>
   <si>
+    <t>7369649485</t>
+  </si>
+  <si>
     <t>VERIFICAR HORAS PARA PLANO DE AÇÃO</t>
   </si>
   <si>
-    <t>24592</t>
+    <t>7369996953</t>
   </si>
   <si>
     <t>Conciliação Relatório para Custeio (Sistema de Corrida) X Requisições (Contabilidade/Materiais)</t>
   </si>
   <si>
-    <t>27756</t>
+    <t>7370010641</t>
   </si>
   <si>
     <t>Correção</t>
@@ -288,64 +321,64 @@
     <t>Erro Relatório Planilha de Custeio</t>
   </si>
   <si>
-    <t>25508</t>
+    <t>7370028574</t>
   </si>
   <si>
     <t>ERRO: Sistema de Corridas - Relatório de Custeio MP</t>
   </si>
   <si>
-    <t>25894</t>
+    <t>7370043886</t>
   </si>
   <si>
     <t>Melhorias de Sistemas Corridas - Cálculo Relatório Planilha de Custeio</t>
   </si>
   <si>
-    <t>27600</t>
+    <t>7333962301</t>
   </si>
   <si>
     <t>Sistema de apontamento de solda Digital tablet</t>
   </si>
   <si>
-    <t>25874</t>
+    <t>7370062680</t>
   </si>
   <si>
     <t>Análise: Conciliação MP - Sistema de Corridas X Requisições 04/2024</t>
   </si>
   <si>
+    <t>7389879423</t>
+  </si>
+  <si>
     <t>Criar relatório (planilha) no portal de notas de entrada para a consulta dos CTEs recebidos x notas lançadas no sistema sem o frete</t>
   </si>
   <si>
-    <t>09/09/2024</t>
-  </si>
-  <si>
-    <t>27520</t>
+    <t>08/09/2024</t>
+  </si>
+  <si>
+    <t>7334019611</t>
   </si>
   <si>
     <t>Relatório de Ofertas Geradas em Excel</t>
   </si>
   <si>
-    <t>27493</t>
+    <t>7334037330</t>
   </si>
   <si>
     <t>ALTERAÇÃO LANÇAMENTO CUSTOS EXTRAS - SISTEMA INVOICE</t>
   </si>
   <si>
-    <t>27455</t>
+    <t>7334273074</t>
   </si>
   <si>
     <t>Impressão Proformas no sistema de Invoice</t>
   </si>
   <si>
-    <t>24686</t>
+    <t>7408378810</t>
   </si>
   <si>
     <t>Atualizar Descrição de Confere para  Carregar</t>
   </si>
   <si>
-    <t>11/09/2024</t>
-  </si>
-  <si>
-    <t>27795</t>
+    <t>7425117058</t>
   </si>
   <si>
     <t>Irog ajustagem</t>
@@ -354,25 +387,25 @@
     <t>13/09/2024</t>
   </si>
   <si>
-    <t>27287</t>
+    <t>7327558686</t>
   </si>
   <si>
     <t>Concilia Relatório Planilha Custeio - Sistemas de Corridas - Análise</t>
   </si>
   <si>
-    <t>27662</t>
+    <t>7331962700</t>
   </si>
   <si>
     <t>Bloqueio programação moldagem com CPP bloqueado</t>
   </si>
   <si>
-    <t>27333</t>
+    <t>7331978254</t>
   </si>
   <si>
     <t>Sistema de Cadastro de modelos - Parte Flavio</t>
   </si>
   <si>
-    <t>27782</t>
+    <t>7382169218</t>
   </si>
   <si>
     <t>Alinhamento de informações - Projeto cadeia de ajuda</t>
@@ -390,7 +423,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2024-44</t>
+    <t>Ago/2024</t>
   </si>
   <si>
     <t>Base</t>
@@ -1026,27 +1059,27 @@
         <v>22</v>
       </c>
       <c r="J3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>32</v>
       </c>
       <c r="M3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N3" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="O3" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>16</v>
@@ -1073,27 +1106,27 @@
         <v>22</v>
       </c>
       <c r="J4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>32</v>
       </c>
       <c r="M4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N4" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="O4" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>16</v>
@@ -1105,10 +1138,10 @@
         <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>20</v>
@@ -1120,27 +1153,27 @@
         <v>22</v>
       </c>
       <c r="J5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>32</v>
       </c>
       <c r="M5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N5" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="N5" s="2" t="s">
+      <c r="O5" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
@@ -1152,10 +1185,10 @@
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>20</v>
@@ -1167,27 +1200,27 @@
         <v>22</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N6" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="N6" s="2" t="s">
+      <c r="O6" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
@@ -1199,10 +1232,10 @@
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>20</v>
@@ -1214,10 +1247,10 @@
         <v>22</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>25</v>
@@ -1226,15 +1259,15 @@
         <v>26</v>
       </c>
       <c r="N7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O7" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
@@ -1246,10 +1279,10 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>20</v>
@@ -1261,27 +1294,27 @@
         <v>22</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N8" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="N8" s="2" t="s">
+      <c r="O8" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
@@ -1293,10 +1326,10 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>20</v>
@@ -1308,10 +1341,10 @@
         <v>22</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>25</v>
@@ -1320,15 +1353,15 @@
         <v>26</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
@@ -1340,25 +1373,25 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J10" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>25</v>
@@ -1367,15 +1400,15 @@
         <v>26</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
@@ -1387,10 +1420,10 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>20</v>
@@ -1402,10 +1435,10 @@
         <v>22</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>25</v>
@@ -1414,15 +1447,15 @@
         <v>26</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -1434,10 +1467,10 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>20</v>
@@ -1449,10 +1482,10 @@
         <v>22</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>25</v>
@@ -1461,7 +1494,7 @@
         <v>26</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="O12" s="2" t="s">
         <v>28</v>
@@ -1469,7 +1502,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
@@ -1481,10 +1514,10 @@
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>20</v>
@@ -1499,7 +1532,7 @@
         <v>23</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>25</v>
@@ -1516,7 +1549,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
@@ -1528,10 +1561,10 @@
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>20</v>
@@ -1543,7 +1576,7 @@
         <v>22</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>24</v>
@@ -1555,7 +1588,7 @@
         <v>26</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>28</v>
@@ -1563,7 +1596,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
@@ -1575,10 +1608,10 @@
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>20</v>
@@ -1590,7 +1623,7 @@
         <v>22</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>24</v>
@@ -1602,7 +1635,7 @@
         <v>26</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="O15" s="2" t="s">
         <v>28</v>
@@ -1610,7 +1643,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -1622,10 +1655,10 @@
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>20</v>
@@ -1637,7 +1670,7 @@
         <v>22</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>24</v>
@@ -1649,7 +1682,7 @@
         <v>26</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="O16" s="2" t="s">
         <v>28</v>
@@ -1657,7 +1690,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
@@ -1669,10 +1702,10 @@
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>20</v>
@@ -1684,10 +1717,10 @@
         <v>22</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>25</v>
@@ -1696,7 +1729,7 @@
         <v>26</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="O17" s="2" t="s">
         <v>28</v>
@@ -1704,37 +1737,37 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J18" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>58</v>
-      </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>25</v>
@@ -1743,7 +1776,7 @@
         <v>26</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="O18" s="2" t="s">
         <v>28</v>
@@ -1751,7 +1784,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
@@ -1763,10 +1796,10 @@
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>20</v>
@@ -1778,10 +1811,10 @@
         <v>22</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>25</v>
@@ -1790,7 +1823,7 @@
         <v>26</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>28</v>
@@ -1798,7 +1831,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
@@ -1810,10 +1843,10 @@
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>20</v>
@@ -1825,10 +1858,10 @@
         <v>22</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>25</v>
@@ -1837,7 +1870,7 @@
         <v>26</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="O20" s="2" t="s">
         <v>28</v>
@@ -1845,7 +1878,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
@@ -1857,10 +1890,10 @@
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>20</v>
@@ -1872,10 +1905,10 @@
         <v>22</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>25</v>
@@ -1884,7 +1917,7 @@
         <v>26</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="O21" s="2" t="s">
         <v>28</v>
@@ -1892,7 +1925,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>15</v>
+        <v>81</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
@@ -1904,10 +1937,10 @@
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>20</v>
@@ -1919,7 +1952,7 @@
         <v>22</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>24</v>
@@ -1931,15 +1964,15 @@
         <v>26</v>
       </c>
       <c r="N22" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O22" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="O22" s="2" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
@@ -1951,10 +1984,10 @@
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>20</v>
@@ -1966,10 +1999,10 @@
         <v>22</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>25</v>
@@ -1978,7 +2011,7 @@
         <v>26</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="O23" s="2" t="s">
         <v>28</v>
@@ -1986,7 +2019,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
@@ -1998,10 +2031,10 @@
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>20</v>
@@ -2013,10 +2046,10 @@
         <v>22</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>25</v>
@@ -2025,7 +2058,7 @@
         <v>26</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="O24" s="2" t="s">
         <v>28</v>
@@ -2033,7 +2066,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
@@ -2045,10 +2078,10 @@
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>20</v>
@@ -2060,7 +2093,7 @@
         <v>22</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>24</v>
@@ -2072,15 +2105,15 @@
         <v>26</v>
       </c>
       <c r="N25" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O25" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="O25" s="2" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
@@ -2092,10 +2125,10 @@
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>20</v>
@@ -2107,10 +2140,10 @@
         <v>22</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>25</v>
@@ -2119,15 +2152,15 @@
         <v>26</v>
       </c>
       <c r="N26" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O26" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="O26" s="2" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
@@ -2139,10 +2172,10 @@
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>20</v>
@@ -2154,19 +2187,19 @@
         <v>22</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>93</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="M27" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="O27" s="2" t="s">
         <v>28</v>
@@ -2174,7 +2207,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
@@ -2186,10 +2219,10 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>20</v>
@@ -2201,10 +2234,10 @@
         <v>22</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>25</v>
@@ -2213,15 +2246,15 @@
         <v>26</v>
       </c>
       <c r="N28" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O28" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="O28" s="2" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
@@ -2233,10 +2266,10 @@
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>20</v>
@@ -2248,10 +2281,10 @@
         <v>22</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>25</v>
@@ -2260,30 +2293,30 @@
         <v>26</v>
       </c>
       <c r="N29" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O29" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="O29" s="2" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>20</v>
@@ -2295,10 +2328,10 @@
         <v>22</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>25</v>
@@ -2307,30 +2340,30 @@
         <v>26</v>
       </c>
       <c r="N30" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O30" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="O30" s="2" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>20</v>
@@ -2342,10 +2375,10 @@
         <v>22</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>25</v>
@@ -2354,15 +2387,15 @@
         <v>26</v>
       </c>
       <c r="N31" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O31" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="O31" s="2" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
@@ -2374,10 +2407,10 @@
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>20</v>
@@ -2389,10 +2422,10 @@
         <v>22</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>25</v>
@@ -2401,15 +2434,15 @@
         <v>26</v>
       </c>
       <c r="N32" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O32" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="O32" s="2" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
@@ -2421,10 +2454,10 @@
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>20</v>
@@ -2436,10 +2469,10 @@
         <v>22</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>25</v>
@@ -2448,7 +2481,7 @@
         <v>26</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="O33" s="2" t="s">
         <v>28</v>
@@ -2456,7 +2489,7 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>16</v>
@@ -2468,10 +2501,10 @@
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>20</v>
@@ -2483,7 +2516,7 @@
         <v>22</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K34" s="2" t="s">
         <v>24</v>
@@ -2495,15 +2528,15 @@
         <v>26</v>
       </c>
       <c r="N34" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O34" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="O34" s="2" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>15</v>
+        <v>110</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>16</v>
@@ -2515,10 +2548,10 @@
         <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>20</v>
@@ -2530,10 +2563,10 @@
         <v>22</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>100</v>
+        <v>51</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>24</v>
+        <v>112</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>25</v>
@@ -2542,15 +2575,15 @@
         <v>26</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>16</v>
@@ -2562,10 +2595,10 @@
         <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>20</v>
@@ -2577,10 +2610,10 @@
         <v>22</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>25</v>
@@ -2589,7 +2622,7 @@
         <v>26</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="O36" s="2" t="s">
         <v>28</v>
@@ -2597,7 +2630,7 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>16</v>
@@ -2609,10 +2642,10 @@
         <v>18</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>20</v>
@@ -2624,10 +2657,10 @@
         <v>22</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>25</v>
@@ -2636,7 +2669,7 @@
         <v>26</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="O37" s="2" t="s">
         <v>28</v>
@@ -2644,7 +2677,7 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>16</v>
@@ -2656,10 +2689,10 @@
         <v>18</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>20</v>
@@ -2671,10 +2704,10 @@
         <v>22</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>25</v>
@@ -2683,7 +2716,7 @@
         <v>26</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="O38" s="2" t="s">
         <v>28</v>
@@ -2691,7 +2724,7 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>16</v>
@@ -2703,10 +2736,10 @@
         <v>18</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>20</v>
@@ -2718,10 +2751,10 @@
         <v>22</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>25</v>
@@ -2730,15 +2763,15 @@
         <v>26</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>16</v>
@@ -2750,10 +2783,10 @@
         <v>18</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>20</v>
@@ -2765,10 +2798,10 @@
         <v>22</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>25</v>
@@ -2777,15 +2810,15 @@
         <v>26</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>16</v>
@@ -2797,10 +2830,10 @@
         <v>18</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>20</v>
@@ -2812,10 +2845,10 @@
         <v>22</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>25</v>
@@ -2824,7 +2857,7 @@
         <v>26</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="O41" s="2" t="s">
         <v>28</v>
@@ -2832,7 +2865,7 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>16</v>
@@ -2844,10 +2877,10 @@
         <v>18</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>20</v>
@@ -2859,19 +2892,19 @@
         <v>22</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="M42" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="O42" s="2" t="s">
         <v>28</v>
@@ -2879,7 +2912,7 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>16</v>
@@ -2891,10 +2924,10 @@
         <v>18</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>20</v>
@@ -2906,19 +2939,19 @@
         <v>22</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="M43" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="O43" s="2" t="s">
         <v>28</v>
@@ -2926,7 +2959,7 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>16</v>
@@ -2938,13 +2971,13 @@
         <v>18</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>21</v>
@@ -2953,10 +2986,10 @@
         <v>22</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>24</v>
+        <v>112</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>25</v>
@@ -2965,10 +2998,10 @@
         <v>26</v>
       </c>
       <c r="N44" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O44" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="O44" s="2" t="s">
-        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -2984,23 +3017,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="B2" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="D2" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="E2" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -3008,16 +3041,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -3028,7 +3061,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>0</v>
+        <v>9.42</v>
       </c>
       <c r="J5" s="4">
         <v>1</v>
@@ -3036,7 +3069,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -3049,7 +3082,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="K23">
         <v>3</v>
@@ -3057,7 +3090,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -3088,12 +3121,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="B2">
         <v>43</v>
@@ -3107,7 +3140,7 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0</v>
+        <v>9.42</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -3117,25 +3150,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -3152,13 +3185,13 @@
         <v>41</v>
       </c>
       <c r="G10" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -3170,21 +3203,21 @@
         <v>35</v>
       </c>
       <c r="P10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q10">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="E11">
         <v>2</v>
       </c>
       <c r="G11" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -3193,7 +3226,7 @@
         <v>26</v>
       </c>
       <c r="K11">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="M11" t="s">
         <v>32</v>
@@ -3202,10 +3235,10 @@
         <v>3</v>
       </c>
       <c r="P11" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="Q11">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="7:17" x14ac:dyDescent="0.25">
@@ -3216,13 +3249,13 @@
         <v>42</v>
       </c>
       <c r="J12" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="K12">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -3231,38 +3264,32 @@
         <v>27</v>
       </c>
       <c r="Q12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="7:17" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G13" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N13">
         <v>2</v>
       </c>
-      <c r="P13" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q13">
-        <v>19</v>
-      </c>
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="N14">
         <v>3</v>
@@ -3270,7 +3297,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -3278,7 +3305,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -3286,7 +3313,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -3294,10 +3321,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -3305,7 +3332,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -3313,142 +3340,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>0</v>
+        <v>656</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>656</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>656</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>656</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>656</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
